--- a/price/price-fanline.xlsx
+++ b/price/price-fanline.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +29,10 @@
       <b val="1"/>
       <color rgb="002F7D46"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
     </font>
     <font>
       <b val="1"/>
@@ -79,14 +83,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,13 +457,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,14 +476,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Прайс-лист от 03.08.2026</t>
+          <t>Прайс-лист от 04.08.2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Телефон: +7 950 646-09-53   ·   Почта: mezdudelom73@gmail.com</t>
+          <t>Связь: мессенджер MAX  ·  Почта: mezdudelom73@gmail.com</t>
         </is>
       </c>
     </row>
@@ -489,176 +494,183 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Материал</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Цена за м³, ₽</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Цена за мешок, ₽</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Примечание</t>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Минимальный заказ с доставкой: 3 м³. Меньший объём — самовывозом.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Цена за м³, ₽</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Цена за мешок, ₽</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
           <t>Чернозём</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B8" s="4" t="n">
         <v>850</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>под грядки, газон, теплицу</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Перегной</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B9" s="4" t="n">
         <v>1100</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C9" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>перепревший, под посадку</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Навоз коровий</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B10" s="4" t="n">
         <v>900</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C10" s="4" t="n">
         <v>130</v>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>свежий и перепревший</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Навоз конский</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="4" t="n">
         <v>1200</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C11" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>под тёплые грядки</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Торф</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B12" s="4" t="n">
         <v>950</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C12" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>низинный и верховой</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Опилки</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B13" s="4" t="n">
         <v>600</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C13" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>хвойные и лиственные</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Плодородный грунт</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B14" s="4" t="n">
         <v>750</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C14" s="4" t="n">
         <v>110</v>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>смесь под газон и отсыпку</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Торфогрунт</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B15" s="4" t="n">
         <v>900</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>130</v>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>готовая смесь под рассаду</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Цены ориентировочные. Точную стоимость с доставкой в ваш район называем по заявке.</t>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Цены ориентировочные. Точную стоимость с доставкой называем по заявке в MAX.</t>
         </is>
       </c>
     </row>

--- a/price/price-fanline.xlsx
+++ b/price/price-fanline.xlsx
@@ -490,7 +490,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Пн-Сб, 8:00-20:00. Оплата любая: наличными, картой или переводом, после выгрузки.</t>
+          <t>Круглосуточно, без выходных. Оплата любая: наличными, картой или переводом, после выгрузки.</t>
         </is>
       </c>
     </row>

--- a/price/price-fanline.xlsx
+++ b/price/price-fanline.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Прайс-лист" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Прайс" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,22 +26,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="002F7D46"/>
-      <sz val="14"/>
+      <color rgb="001F3B2C"/>
+      <sz val="16"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00B45309"/>
+      <name val="Calibri"/>
+      <color rgb="001F3B2C"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="001F3B2C"/>
+      <sz val="11"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="005B6B60"/>
-      <sz val="10"/>
+      <name val="Calibri"/>
+      <color rgb="001F3B2C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3B2C"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="3">
@@ -53,7 +63,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F7D46"/>
+        <fgColor rgb="00E8F1EA"/>
       </patternFill>
     </fill>
   </fills>
@@ -67,31 +77,48 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D8E0D8"/>
+        <color rgb="00C9D8CD"/>
       </left>
       <right style="thin">
-        <color rgb="00D8E0D8"/>
+        <color rgb="00C9D8CD"/>
       </right>
       <top style="thin">
-        <color rgb="00D8E0D8"/>
+        <color rgb="00C9D8CD"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D8E0D8"/>
+        <color rgb="00C9D8CD"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -457,13 +484,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,203 +500,423 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Прайс-лист от 04.08.2026</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Прайс-лист от 23.08.2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Связь: мессенджер MAX  ·  Почта: mezdudelom73@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Круглосуточно, без выходных. Оплата любая: наличными, картой или переводом, после выгрузки.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Минимальный заказ с доставкой: 3 м³. Меньший объём — самовывозом.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Материал</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Цена за м³, ₽</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Цена за мешок, ₽</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Примечание</t>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Минимальный заказ 3 м³: меньше не возим, рейс не окупается. Возим только навалом, фасовки в мешках нет.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Цена за м³, ₽</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
           <t>Чернозём</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>850</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>от 850</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>под грядки, газон, теплицу</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Перегной</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>от 1100</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>перепревший, под посадку</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Навоз коровий</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>900</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>от 900</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>свежий и перепревший</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Навоз конский</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>от 1200</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>под тёплые грядки</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Торф</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>от 950</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>низинный и верховой</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Опилки</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>от 600</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>хвойные и лиственные</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Плодородный грунт</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>от 750</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>смесь под газон и отсыпку</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Торфогрунт</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>от 900</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>готовая смесь под рассаду</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Доставка</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>95 ₽ за километр из Верхней Пышмы, рейс считается туда и обратно</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Стоимость рейса не зависит от загрузки кузова, поэтому чем больше объём, тем дешевле выходит кубометр.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Куда</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Плечо, км</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Рейс, ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Верхняя Пышма</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="7" t="n">
         <v>950</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>низинный и верховой</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Опилки</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>600</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>хвойные и лиственные</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Плодородный грунт</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="C14" s="4" t="n">
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Среднеуральск</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Берёзовский</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>4750</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Арамиль</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Верхнее Дуброво</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>8550</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Белоярский</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Заречный</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>10450</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Первоуральск</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>10450</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Ревда</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>12350</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Сысерть</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>12350</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Дегтярск</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>13300</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Полевской</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>13300</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Каменск-Уральский</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
         <v>110</v>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>смесь под газон и отсыпку</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Торфогрунт</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>900</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>готовая смесь под рассаду</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Цены ориентировочные. Точную стоимость с доставкой называем по заявке в MAX.</t>
+      <c r="C36" s="7" t="n">
+        <v>20900</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Нижний Тагил</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>23750</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Цены на материал ориентировочные, «от». Точную стоимость с доставкой называем по заявке в MAX, когда знаем объём, адрес и подъезд.</t>
         </is>
       </c>
     </row>

--- a/price/price-fanline.xlsx
+++ b/price/price-fanline.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -502,7 +502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Прайс-лист от 23.08.2026</t>
+          <t>Прайс-лист от 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -632,65 +632,55 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Опилки</t>
+          <t>Плодородный грунт</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>от 600</t>
+          <t>от 750</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>хвойные и лиственные</t>
+          <t>смесь под газон и отсыпку</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Плодородный грунт</t>
+          <t>Торфогрунт</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>от 750</t>
+          <t>от 900</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>смесь под газон и отсыпку</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Торфогрунт</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>от 900</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
           <t>готовая смесь под рассаду</t>
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Доставка</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Доставка</t>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>от 95 ₽ за километр от базы, рейс считается туда и обратно, с подачей машины</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>95 ₽ за километр из Верхней Пышмы, рейс считается туда и обратно</t>
+          <t>Базы разные: земля, торф и торфогрунт грузятся в Курганово (Полевской тракт), перегной и навоз — в Садовом. Плечо в таблице ниже дано для земли; по органике считаем от Садового.</t>
         </is>
       </c>
     </row>
@@ -721,200 +711,343 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Верхняя Пышма</t>
+          <t>Курганово</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>950</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Среднеуральск</t>
+          <t>Полевской тракт</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
         <v>10</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>1900</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Горный Щит</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
         <v>15</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>2850</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Берёзовский</t>
+          <t>Северский</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>4750</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Арамиль</t>
+          <t>Полевской</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>7600</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Верхнее Дуброво</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>8550</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Белоярский</t>
+          <t>Кашино</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>9500</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Заречный</t>
+          <t>Сысерть</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>10450</v>
+        <v>7650</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Первоуральск</t>
+          <t>Верхняя Сысерть</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>10450</v>
+        <v>7650</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Ревда</t>
+          <t>Дегтярск</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>12350</v>
+        <v>7650</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Сысерть</t>
+          <t>Большой Исток</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>12350</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Дегтярск</t>
+          <t>Патруши</t>
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>13300</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Полевской</t>
+          <t>Верхняя Пышма</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>13300</v>
+        <v>9550</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Каменск-Уральский</t>
+          <t>Берёзовский</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>110</v>
+        <v>45</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>20900</v>
+        <v>9550</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
+          <t>Арамиль</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>9550</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Ревда</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>9550</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Челябинский тракт</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>9550</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Среднеуральск</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Бобровский</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Верхнее Дуброво</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>11450</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Первоуральск</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>11450</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Двуреченск</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>12400</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Белоярский</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>13350</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Заречный</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>13350</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Каменск-Уральский</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>23800</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
           <t>Нижний Тагил</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
-        <v>125</v>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>23750</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="B48" s="7" t="n">
+        <v>165</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>32350</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Цены на материал ориентировочные, «от». Точную стоимость с доставкой называем по заявке в MAX, когда знаем объём, адрес и подъезд.</t>
         </is>

--- a/price/price-fanline.xlsx
+++ b/price/price-fanline.xlsx
@@ -502,7 +502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Прайс-лист от 02.09.2026</t>
+          <t>Прайс-лист от 03.09.2026</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>от 95 ₽ за километр от базы, рейс считается туда и обратно, с подачей машины</t>
+          <t>от 76 ₽ за километр от базы, рейс считается туда и обратно, с подачей машины</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
         <v>5</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>1950</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="24">
@@ -731,7 +731,7 @@
         <v>10</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>2900</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="25">
@@ -744,7 +744,7 @@
         <v>15</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>3850</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="26">
@@ -757,7 +757,7 @@
         <v>20</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>4800</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="27">
@@ -770,7 +770,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>5750</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="28">
@@ -783,7 +783,7 @@
         <v>30</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>6700</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="29">
@@ -796,7 +796,7 @@
         <v>30</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>6700</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="30">
@@ -809,7 +809,7 @@
         <v>35</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>7650</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="31">
@@ -822,7 +822,7 @@
         <v>35</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>7650</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="32">
@@ -835,7 +835,7 @@
         <v>35</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>7650</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="33">
@@ -848,7 +848,7 @@
         <v>40</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>8600</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="34">
@@ -861,7 +861,7 @@
         <v>40</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>8600</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="35">
@@ -874,7 +874,7 @@
         <v>45</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>9550</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="36">
@@ -887,7 +887,7 @@
         <v>45</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>9550</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="37">
@@ -900,7 +900,7 @@
         <v>45</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>9550</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="38">
@@ -913,7 +913,7 @@
         <v>45</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>9550</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="39">
@@ -926,7 +926,7 @@
         <v>45</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>9550</v>
+        <v>7840</v>
       </c>
     </row>
     <row r="40">
@@ -939,7 +939,7 @@
         <v>50</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>10500</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="41">
@@ -952,7 +952,7 @@
         <v>50</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>10500</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="42">
@@ -965,7 +965,7 @@
         <v>55</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>11450</v>
+        <v>9360</v>
       </c>
     </row>
     <row r="43">
@@ -978,7 +978,7 @@
         <v>55</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>11450</v>
+        <v>9360</v>
       </c>
     </row>
     <row r="44">
@@ -991,7 +991,7 @@
         <v>60</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>12400</v>
+        <v>10120</v>
       </c>
     </row>
     <row r="45">
@@ -1004,7 +1004,7 @@
         <v>65</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>13350</v>
+        <v>10880</v>
       </c>
     </row>
     <row r="46">
@@ -1017,7 +1017,7 @@
         <v>65</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>13350</v>
+        <v>10880</v>
       </c>
     </row>
     <row r="47">
@@ -1030,7 +1030,7 @@
         <v>120</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>23800</v>
+        <v>19240</v>
       </c>
     </row>
     <row r="48">
@@ -1043,7 +1043,7 @@
         <v>165</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>32350</v>
+        <v>26080</v>
       </c>
     </row>
     <row r="50">
